--- a/output/register.xlsx
+++ b/output/register.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Document Details" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Document Details" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Risk Register" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -597,7 +597,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O10"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -719,7 +719,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>sample_app\app.py:9</t>
+          <t>sample_app/app.py:9</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -794,7 +794,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>sample_app\app.py:12</t>
+          <t>sample_app/app.py:12</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>sample_app\app.py:17</t>
+          <t>sample_app/app.py:17</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>sample_app\app.py:23</t>
+          <t>sample_app/app.py:23</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>sample_app\app.py:30</t>
+          <t>sample_app/app.py:30</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>sample_app\app.py:35</t>
+          <t>sample_app/app.py:35</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>sample_app\app.py:40</t>
+          <t>sample_app/app.py:40</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>sample_app\app.py:46</t>
+          <t>sample_app/app.py:46</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -1298,6 +1298,81 @@
       <c r="O10" s="3" t="inlineStr">
         <is>
           <t>bandit</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>CTRL-0001</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>COMPLIANCE</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>OpenSSL 3.0.13 30 Jan 2024 (Library: OpenSSL 3.0.13 30 Jan 2024)</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>openssl version (over SSH or local fallback)</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>CWE-327</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>Low (6)</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>Planned on-cycle fix; monitored under vulnerability management.</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>CTRL-SSH-001</t>
         </is>
       </c>
     </row>

--- a/output/register.xlsx
+++ b/output/register.xlsx
@@ -597,7 +597,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:O12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1304,45 +1304,45 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>CTRL-0001</t>
+          <t>TMT-001</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>COMPLIANCE</t>
+          <t>TMT</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>OpenSSL 3.0.13 30 Jan 2024 (Library: OpenSSL 3.0.13 30 Jan 2024)</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>openssl version (over SSH or local fallback)</t>
+          <t>command -v clevis || echo missing</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>CWE-327</t>
+          <t>CWE-311</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>Low (6)</t>
+          <t>Moderate (12)</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1352,27 +1352,102 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L11" s="6" t="inlineStr">
+        <is>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>Acceptable</t>
-        </is>
-      </c>
-      <c r="N11" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>Acceptable (BRA)</t>
+        </is>
+      </c>
+      <c r="N11" s="6" t="inlineStr">
+        <is>
+          <t>Applicable</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>CTRL-SSH-001</t>
+          <t>TMT-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>TMT-002</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>TMT</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>command -v auditctl || echo missing</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>CWE-778</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>Moderate (9)</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>Planned on-cycle fix; monitored under vulnerability management.</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L12" s="6" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>Acceptable (BRA)</t>
+        </is>
+      </c>
+      <c r="N12" s="6" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>TMT-002</t>
         </is>
       </c>
     </row>

--- a/output/register.xlsx
+++ b/output/register.xlsx
@@ -44,7 +44,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -64,6 +64,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F6EBD6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5E0DD"/>
       </patternFill>
     </fill>
   </fills>
@@ -93,7 +98,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -105,6 +110,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -597,7 +605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O12"/>
+  <dimension ref="A1:O18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1304,27 +1312,27 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>TMT-001</t>
+          <t>FND-0009</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>TMT</t>
+          <t>SCA</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>sample-imagelib 1.2.0 out-of-bounds read</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>command -v clevis || echo missing</t>
+          <t>backend/requirements.txt</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>CWE-311</t>
+          <t>CVE-2099-0101</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -1372,34 +1380,34 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>TMT-001</t>
+          <t>grype</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>TMT-002</t>
+          <t>FND-0010</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>TMT</t>
+          <t>SCA</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>sample-webframework 3.0.1 uncontrolled resource consumption</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>command -v auditctl || echo missing</t>
+          <t>frontend/package-lock.json</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>CWE-778</t>
+          <t>CVE-2099-0102</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -1446,6 +1454,456 @@
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>grype</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>FND-0011</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>DAST</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>object-level authorization not enforced (IDOR) on sample endpoint</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>GET /api/items/{id}</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>CWE-639</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>High (15)</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>Planned on-cycle fix; monitored under vulnerability management.</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L13" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="N13" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>zap</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>FND-0012</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>DAST</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>websocket endpoint reachable without authentication</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>WS /realtime</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>CWE-306</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>Moderate (9)</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>Planned on-cycle fix; monitored under vulnerability management.</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L14" s="6" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>Acceptable (BRA)</t>
+        </is>
+      </c>
+      <c r="N14" s="6" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t>zap</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>FND-0013</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>FUZZ</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>out-of-range integer causes unhandled HTTP 500</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>POST /api/items (quantity)</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>CWE-20</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>Low (6)</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>Planned on-cycle fix; monitored under vulnerability management.</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t>schemathesis</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>FND-0014</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>ASA</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>management console reachable from the application network</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>tcp/8443 admin console</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>CWE-200</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>Moderate (9)</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>Planned on-cycle fix; monitored under vulnerability management.</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L16" s="6" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>Acceptable (BRA)</t>
+        </is>
+      </c>
+      <c r="N16" s="6" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>nmap</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>TMT-001</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>TMT</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>command -v clevis || echo missing</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>CWE-311</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>Moderate (12)</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>Planned on-cycle fix; monitored under vulnerability management.</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L17" s="6" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>Acceptable (BRA)</t>
+        </is>
+      </c>
+      <c r="N17" s="6" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>TMT-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>TMT-002</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>TMT</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>command -v auditctl || echo missing</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>CWE-778</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>Moderate (9)</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>Planned on-cycle fix; monitored under vulnerability management.</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L18" s="6" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>Acceptable (BRA)</t>
+        </is>
+      </c>
+      <c r="N18" s="6" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
         <is>
           <t>TMT-002</t>
         </is>

--- a/output/register.xlsx
+++ b/output/register.xlsx
@@ -605,7 +605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O18"/>
+  <dimension ref="A1:O64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>sample_app/app.py:9</t>
+          <t>./sample_app/app.py:9</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -802,7 +802,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>sample_app/app.py:12</t>
+          <t>./sample_app/app.py:12</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>sample_app/app.py:17</t>
+          <t>./sample_app/app.py:17</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>sample_app/app.py:23</t>
+          <t>./sample_app/app.py:23</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>sample_app/app.py:30</t>
+          <t>./sample_app/app.py:30</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>sample_app/app.py:35</t>
+          <t>./sample_app/app.py:35</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>sample_app/app.py:40</t>
+          <t>./sample_app/app.py:40</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>sample_app/app.py:46</t>
+          <t>./sample_app/app.py:46</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -1317,70 +1317,70 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>SCA</t>
+          <t>DAST</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>sample-imagelib 1.2.0 out-of-bounds read</t>
+          <t>object-level authorization not enforced (sonoA read sonoB's exam)</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>backend/requirements.txt</t>
+          <t>GET /api/exams/{id}</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>CVE-2099-0101</t>
+          <t>CWE-639</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>High (15)</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>Planned on-cycle fix; monitored under vulnerability management.</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L11" s="7" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>Moderate (12)</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>Planned on-cycle fix; monitored under vulnerability management.</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="L11" s="6" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>Acceptable (BRA)</t>
-        </is>
-      </c>
-      <c r="N11" s="6" t="inlineStr">
-        <is>
-          <t>Applicable</t>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="N11" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>grype</t>
+          <t>dast-recipes</t>
         </is>
       </c>
     </row>
@@ -1392,22 +1392,22 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>SCA</t>
+          <t>DAST</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>sample-webframework 3.0.1 uncontrolled resource consumption</t>
+          <t>frame/PHI endpoint reachable without authentication</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>frontend/package-lock.json</t>
+          <t>GET /api/frame/{id}</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>CVE-2099-0102</t>
+          <t>CWE-306</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>grype</t>
+          <t>dast-recipes</t>
         </is>
       </c>
     </row>
@@ -1472,22 +1472,22 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>object-level authorization not enforced (IDOR) on sample endpoint</t>
+          <t>empty/whitespace patient identity accepted (unattributable record)</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>GET /api/items/{id}</t>
+          <t>POST /api/patient</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>CWE-639</t>
+          <t>CWE-20</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -1496,11 +1496,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>High (15)</t>
+          <t>Moderate (9)</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1513,24 +1513,24 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="L13" s="7" t="inlineStr">
-        <is>
-          <t>High</t>
+      <c r="L13" s="6" t="inlineStr">
+        <is>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>Acceptable</t>
-        </is>
-      </c>
-      <c r="N13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>Acceptable (BRA)</t>
+        </is>
+      </c>
+      <c r="N13" s="6" t="inlineStr">
+        <is>
+          <t>Applicable</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>zap</t>
+          <t>dast-recipes</t>
         </is>
       </c>
     </row>
@@ -1547,22 +1547,22 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>websocket endpoint reachable without authentication</t>
+          <t>duplicate patientId silently overwrites demographics</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>WS /realtime</t>
+          <t>POST /api/patient</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>CWE-306</t>
+          <t>CWE-20</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
@@ -1571,11 +1571,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>Moderate (9)</t>
+          <t>Moderate (12)</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>zap</t>
+          <t>dast-recipes</t>
         </is>
       </c>
     </row>
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>out-of-range integer causes unhandled HTTP 500</t>
+          <t>integer far out of range -&gt; unhandled server error (HTTP 500)</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>POST /api/items (quantity)</t>
+          <t>/api/qty/99999999999999</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>CWE-20</t>
+          <t>CWE-190</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>schemathesis</t>
+          <t>fuzzer</t>
         </is>
       </c>
     </row>
@@ -1692,27 +1692,27 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>ASA</t>
+          <t>FUZZ</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>management console reachable from the application network</t>
+          <t>wrong type where integer expected -&gt; unhandled server error (HTTP 500)</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>tcp/8443 admin console</t>
+          <t>/api/qty/abc</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>CWE-200</t>
+          <t>CWE-20</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
@@ -1721,11 +1721,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>Moderate (9)</t>
+          <t>Low (6)</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1738,56 +1738,56 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="L16" s="6" t="inlineStr">
-        <is>
-          <t>Moderate</t>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>Acceptable (BRA)</t>
-        </is>
-      </c>
-      <c r="N16" s="6" t="inlineStr">
-        <is>
-          <t>Applicable</t>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>nmap</t>
+          <t>fuzzer</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>TMT-001</t>
+          <t>FND-0015</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>TMT</t>
+          <t>ASA</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>missing Content-Security-Policy header</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>command -v clevis || echo missing</t>
+          <t>http://127.0.0.1:8099 response headers</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>CWE-311</t>
+          <t>CWE-693</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -1796,11 +1796,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>Moderate (12)</t>
+          <t>Moderate (9)</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1830,80 +1830,3358 @@
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>TMT-001</t>
+          <t>surface-scan</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
+          <t>FND-0016</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>ASA</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>missing HSTS header</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>http://127.0.0.1:8099 response headers</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>CWE-319</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>Low (6)</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>Planned on-cycle fix; monitored under vulnerability management.</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t>surface-scan</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>FND-0017</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>ASA</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>missing X-Content-Type-Options header</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>http://127.0.0.1:8099 response headers</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>CWE-693</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>Low (6)</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>Planned on-cycle fix; monitored under vulnerability management.</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t>surface-scan</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>FND-0018</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>jinja2 2.11.2: PYSEC-2021-66 (2.11.3)</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>jinja2==2.11.2</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr"/>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>Moderate (12)</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>Planned on-cycle fix; monitored under vulnerability management.</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L20" s="6" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>Acceptable (BRA)</t>
+        </is>
+      </c>
+      <c r="N20" s="6" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t>pip-audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>FND-0019</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>jinja2 2.11.2: PYSEC-2026-1473 (3.1.3)</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>jinja2==2.11.2</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr"/>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>Moderate (12)</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>Planned on-cycle fix; monitored under vulnerability management.</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L21" s="6" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>Acceptable (BRA)</t>
+        </is>
+      </c>
+      <c r="N21" s="6" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>pip-audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>FND-0020</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>jinja2 2.11.2: PYSEC-2026-1471 (3.1.6)</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>jinja2==2.11.2</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr"/>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>Moderate (12)</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>Planned on-cycle fix; monitored under vulnerability management.</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L22" s="6" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>Acceptable (BRA)</t>
+        </is>
+      </c>
+      <c r="N22" s="6" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="inlineStr">
+        <is>
+          <t>pip-audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>FND-0021</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>jinja2 2.11.2: PYSEC-2026-1474 (3.1.4)</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>jinja2==2.11.2</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr"/>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>Moderate (12)</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>Planned on-cycle fix; monitored under vulnerability management.</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L23" s="6" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>Acceptable (BRA)</t>
+        </is>
+      </c>
+      <c r="N23" s="6" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+      <c r="O23" s="3" t="inlineStr">
+        <is>
+          <t>pip-audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>FND-0022</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>jinja2 2.11.2: PYSEC-2026-1475 (3.1.5)</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>jinja2==2.11.2</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr"/>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>Moderate (12)</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>Planned on-cycle fix; monitored under vulnerability management.</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L24" s="6" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>Acceptable (BRA)</t>
+        </is>
+      </c>
+      <c r="N24" s="6" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t>pip-audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>FND-0023</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>pyyaml 5.3: PYSEC-2020-96 (5.3.1)</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>pyyaml==5.3</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr"/>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>Moderate (12)</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>Planned on-cycle fix; monitored under vulnerability management.</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L25" s="6" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>Acceptable (BRA)</t>
+        </is>
+      </c>
+      <c r="N25" s="6" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t>pip-audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>FND-0024</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>pyyaml 5.3: PYSEC-2021-142 (5.4)</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>pyyaml==5.3</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr"/>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>Moderate (12)</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>Planned on-cycle fix; monitored under vulnerability management.</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L26" s="6" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>Acceptable (BRA)</t>
+        </is>
+      </c>
+      <c r="N26" s="6" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+      <c r="O26" s="3" t="inlineStr">
+        <is>
+          <t>pip-audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>FND-0025</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>pyyaml 5.3: PYSEC-2021-142 (5.4)</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>pyyaml==5.3</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr"/>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>Moderate (12)</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>Planned on-cycle fix; monitored under vulnerability management.</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L27" s="6" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>Acceptable (BRA)</t>
+        </is>
+      </c>
+      <c r="N27" s="6" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t>pip-audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>FND-0026</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>pyyaml 5.3: PYSEC-2020-96 (5.3.1)</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>pyyaml==5.3</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr"/>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>Moderate (12)</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>Planned on-cycle fix; monitored under vulnerability management.</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L28" s="6" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>Acceptable (BRA)</t>
+        </is>
+      </c>
+      <c r="N28" s="6" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+      <c r="O28" s="3" t="inlineStr">
+        <is>
+          <t>pip-audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>FND-0027</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>requests 2.19.0: PYSEC-2018-28 (2.20.0)</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>requests==2.19.0</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr"/>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>Moderate (12)</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>Planned on-cycle fix; monitored under vulnerability management.</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L29" s="6" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>Acceptable (BRA)</t>
+        </is>
+      </c>
+      <c r="N29" s="6" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t>pip-audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>FND-0028</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>requests 2.19.0: PYSEC-2023-74 (2.31.0)</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>requests==2.19.0</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr"/>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>Moderate (12)</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>Planned on-cycle fix; monitored under vulnerability management.</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L30" s="6" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>Acceptable (BRA)</t>
+        </is>
+      </c>
+      <c r="N30" s="6" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+      <c r="O30" s="3" t="inlineStr">
+        <is>
+          <t>pip-audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>FND-0029</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>requests 2.19.0: PYSEC-2023-74 (2.31.0)</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>requests==2.19.0</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr"/>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>Moderate (12)</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>Planned on-cycle fix; monitored under vulnerability management.</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L31" s="6" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>Acceptable (BRA)</t>
+        </is>
+      </c>
+      <c r="N31" s="6" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+      <c r="O31" s="3" t="inlineStr">
+        <is>
+          <t>pip-audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>FND-0030</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>requests 2.19.0: PYSEC-2026-1873 (2.32.0)</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>requests==2.19.0</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr"/>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>Moderate (12)</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>Planned on-cycle fix; monitored under vulnerability management.</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L32" s="6" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>Acceptable (BRA)</t>
+        </is>
+      </c>
+      <c r="N32" s="6" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="inlineStr">
+        <is>
+          <t>pip-audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>FND-0031</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>requests 2.19.0: PYSEC-2026-1872 (2.32.4)</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>requests==2.19.0</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr"/>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>Moderate (12)</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>Planned on-cycle fix; monitored under vulnerability management.</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L33" s="6" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>Acceptable (BRA)</t>
+        </is>
+      </c>
+      <c r="N33" s="6" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+      <c r="O33" s="3" t="inlineStr">
+        <is>
+          <t>pip-audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>FND-0032</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>requests 2.19.0: PYSEC-2026-2275 (2.33.0)</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>requests==2.19.0</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr"/>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>Moderate (12)</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>Planned on-cycle fix; monitored under vulnerability management.</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L34" s="6" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>Acceptable (BRA)</t>
+        </is>
+      </c>
+      <c r="N34" s="6" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+      <c r="O34" s="3" t="inlineStr">
+        <is>
+          <t>pip-audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>FND-0033</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>idna 2.7: PYSEC-2024-60 (3.7)</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>idna==2.7</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr"/>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>Moderate (12)</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>Planned on-cycle fix; monitored under vulnerability management.</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L35" s="6" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>Acceptable (BRA)</t>
+        </is>
+      </c>
+      <c r="N35" s="6" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+      <c r="O35" s="3" t="inlineStr">
+        <is>
+          <t>pip-audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>FND-0034</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>idna 2.7: PYSEC-2024-60 (3.7)</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>idna==2.7</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr"/>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>Moderate (12)</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>Planned on-cycle fix; monitored under vulnerability management.</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L36" s="6" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>Acceptable (BRA)</t>
+        </is>
+      </c>
+      <c r="N36" s="6" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+      <c r="O36" s="3" t="inlineStr">
+        <is>
+          <t>pip-audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>FND-0035</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>idna 2.7: PYSEC-2026-215 (3.15)</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>idna==2.7</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr"/>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>Moderate (12)</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>Planned on-cycle fix; monitored under vulnerability management.</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L37" s="6" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>Acceptable (BRA)</t>
+        </is>
+      </c>
+      <c r="N37" s="6" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+      <c r="O37" s="3" t="inlineStr">
+        <is>
+          <t>pip-audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>FND-0036</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>idna 2.7: PYSEC-2026-215 (3.15)</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>idna==2.7</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr"/>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>Moderate (12)</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>Planned on-cycle fix; monitored under vulnerability management.</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L38" s="6" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>Acceptable (BRA)</t>
+        </is>
+      </c>
+      <c r="N38" s="6" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+      <c r="O38" s="3" t="inlineStr">
+        <is>
+          <t>pip-audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>FND-0037</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>urllib3 1.23: PYSEC-2019-133 (1.24.2)</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>urllib3==1.23</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr"/>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>Moderate (12)</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>Planned on-cycle fix; monitored under vulnerability management.</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L39" s="6" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>Acceptable (BRA)</t>
+        </is>
+      </c>
+      <c r="N39" s="6" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+      <c r="O39" s="3" t="inlineStr">
+        <is>
+          <t>pip-audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>FND-0038</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>urllib3 1.23: PYSEC-2019-132 (1.24.3)</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>urllib3==1.23</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr"/>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>Moderate (12)</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>Planned on-cycle fix; monitored under vulnerability management.</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L40" s="6" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>Acceptable (BRA)</t>
+        </is>
+      </c>
+      <c r="N40" s="6" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+      <c r="O40" s="3" t="inlineStr">
+        <is>
+          <t>pip-audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>FND-0039</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>urllib3 1.23: PYSEC-2020-148 (1.25.9)</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>urllib3==1.23</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr"/>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>Moderate (12)</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>Planned on-cycle fix; monitored under vulnerability management.</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L41" s="6" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>Acceptable (BRA)</t>
+        </is>
+      </c>
+      <c r="N41" s="6" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+      <c r="O41" s="3" t="inlineStr">
+        <is>
+          <t>pip-audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>FND-0040</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>urllib3 1.23: PYSEC-2023-192 (1.26.17,2.0.6)</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>urllib3==1.23</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr"/>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>Moderate (12)</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>Planned on-cycle fix; monitored under vulnerability management.</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L42" s="6" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>Acceptable (BRA)</t>
+        </is>
+      </c>
+      <c r="N42" s="6" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+      <c r="O42" s="3" t="inlineStr">
+        <is>
+          <t>pip-audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>FND-0041</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>urllib3 1.23: PYSEC-2023-192 (1.26.17,2.0.6)</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>urllib3==1.23</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr"/>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>Moderate (12)</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>Planned on-cycle fix; monitored under vulnerability management.</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L43" s="6" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>Acceptable (BRA)</t>
+        </is>
+      </c>
+      <c r="N43" s="6" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+      <c r="O43" s="3" t="inlineStr">
+        <is>
+          <t>pip-audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>FND-0042</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>urllib3 1.23: PYSEC-2023-212 (1.26.18,2.0.7)</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>urllib3==1.23</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr"/>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>Moderate (12)</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>Planned on-cycle fix; monitored under vulnerability management.</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L44" s="6" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>Acceptable (BRA)</t>
+        </is>
+      </c>
+      <c r="N44" s="6" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+      <c r="O44" s="3" t="inlineStr">
+        <is>
+          <t>pip-audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>FND-0043</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>urllib3 1.23: PYSEC-2023-207 (1.24.2)</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>urllib3==1.23</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr"/>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>Moderate (12)</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>Planned on-cycle fix; monitored under vulnerability management.</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L45" s="6" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>Acceptable (BRA)</t>
+        </is>
+      </c>
+      <c r="N45" s="6" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+      <c r="O45" s="3" t="inlineStr">
+        <is>
+          <t>pip-audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>FND-0044</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>urllib3 1.23: PYSEC-2023-212 (1.26.18,2.0.7)</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>urllib3==1.23</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr"/>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>Moderate (12)</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>Planned on-cycle fix; monitored under vulnerability management.</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L46" s="6" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>Acceptable (BRA)</t>
+        </is>
+      </c>
+      <c r="N46" s="6" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="inlineStr">
+        <is>
+          <t>pip-audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>FND-0045</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>urllib3 1.23: PYSEC-2026-141 (2.7.0)</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>urllib3==1.23</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr"/>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>Moderate (12)</t>
+        </is>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>Planned on-cycle fix; monitored under vulnerability management.</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L47" s="6" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>Acceptable (BRA)</t>
+        </is>
+      </c>
+      <c r="N47" s="6" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+      <c r="O47" s="3" t="inlineStr">
+        <is>
+          <t>pip-audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>FND-0046</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>urllib3 1.23: PYSEC-2026-1999 (2.5.0)</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>urllib3==1.23</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr"/>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>Moderate (12)</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>Planned on-cycle fix; monitored under vulnerability management.</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L48" s="6" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>Acceptable (BRA)</t>
+        </is>
+      </c>
+      <c r="N48" s="6" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+      <c r="O48" s="3" t="inlineStr">
+        <is>
+          <t>pip-audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>FND-0047</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>urllib3 1.23: PYSEC-2026-1995 (1.26.19,2.2.2)</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>urllib3==1.23</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr"/>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>Moderate (12)</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>Planned on-cycle fix; monitored under vulnerability management.</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L49" s="6" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>Acceptable (BRA)</t>
+        </is>
+      </c>
+      <c r="N49" s="6" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+      <c r="O49" s="3" t="inlineStr">
+        <is>
+          <t>pip-audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>FND-0048</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>urllib3 1.23: PYSEC-2026-1994 (2.6.0)</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>urllib3==1.23</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr"/>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>Moderate (12)</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>Planned on-cycle fix; monitored under vulnerability management.</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L50" s="6" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>Acceptable (BRA)</t>
+        </is>
+      </c>
+      <c r="N50" s="6" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+      <c r="O50" s="3" t="inlineStr">
+        <is>
+          <t>pip-audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>FND-0049</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>urllib3 1.23: PYSEC-2026-1996 (2.6.3)</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>urllib3==1.23</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr"/>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>Moderate (12)</t>
+        </is>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>Planned on-cycle fix; monitored under vulnerability management.</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L51" s="6" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>Acceptable (BRA)</t>
+        </is>
+      </c>
+      <c r="N51" s="6" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+      <c r="O51" s="3" t="inlineStr">
+        <is>
+          <t>pip-audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>FND-0050</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>CBT</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>exploitable in deployment (network-reachable): jinja2 2.11.2: PYSEC-2021-66 (2.1</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>jinja2==2.11.2</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr"/>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>Moderate (12)</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>Planned on-cycle fix; monitored under vulnerability management.</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L52" s="6" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>Acceptable (BRA)</t>
+        </is>
+      </c>
+      <c r="N52" s="6" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+      <c r="O52" s="3" t="inlineStr">
+        <is>
+          <t>closed-box</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>FND-0051</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>CBT</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>exploitable in deployment (network-reachable): jinja2 2.11.2: PYSEC-2026-1473 (3</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>jinja2==2.11.2</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr"/>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H53" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>Moderate (12)</t>
+        </is>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>Planned on-cycle fix; monitored under vulnerability management.</t>
+        </is>
+      </c>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L53" s="6" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>Acceptable (BRA)</t>
+        </is>
+      </c>
+      <c r="N53" s="6" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+      <c r="O53" s="3" t="inlineStr">
+        <is>
+          <t>closed-box</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>FND-0052</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>CBT</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>exploitable in deployment (network-reachable): jinja2 2.11.2: PYSEC-2026-1471 (3</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>jinja2==2.11.2</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr"/>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>Moderate (12)</t>
+        </is>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>Planned on-cycle fix; monitored under vulnerability management.</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L54" s="6" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>Acceptable (BRA)</t>
+        </is>
+      </c>
+      <c r="N54" s="6" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+      <c r="O54" s="3" t="inlineStr">
+        <is>
+          <t>closed-box</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>FND-0053</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>CBT</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>exploitable in deployment (network-reachable): jinja2 2.11.2: PYSEC-2026-1474 (3</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>jinja2==2.11.2</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr"/>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H55" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t>Moderate (12)</t>
+        </is>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>Planned on-cycle fix; monitored under vulnerability management.</t>
+        </is>
+      </c>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L55" s="6" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>Acceptable (BRA)</t>
+        </is>
+      </c>
+      <c r="N55" s="6" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+      <c r="O55" s="3" t="inlineStr">
+        <is>
+          <t>closed-box</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>FND-0054</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>CBT</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>exploitable in deployment (network-reachable): jinja2 2.11.2: PYSEC-2026-1475 (3</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>jinja2==2.11.2</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr"/>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>Moderate (12)</t>
+        </is>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>Planned on-cycle fix; monitored under vulnerability management.</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L56" s="6" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>Acceptable (BRA)</t>
+        </is>
+      </c>
+      <c r="N56" s="6" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+      <c r="O56" s="3" t="inlineStr">
+        <is>
+          <t>closed-box</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>FND-0055</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>CBT</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>exploitable in deployment (network-reachable): requests 2.19.0: PYSEC-2018-28 (2</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>requests==2.19.0</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr"/>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H57" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>Moderate (12)</t>
+        </is>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>Planned on-cycle fix; monitored under vulnerability management.</t>
+        </is>
+      </c>
+      <c r="K57" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L57" s="6" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>Acceptable (BRA)</t>
+        </is>
+      </c>
+      <c r="N57" s="6" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+      <c r="O57" s="3" t="inlineStr">
+        <is>
+          <t>closed-box</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>FND-0056</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>CBT</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>exploitable in deployment (network-reachable): requests 2.19.0: PYSEC-2023-74 (2</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>requests==2.19.0</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr"/>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I58" s="3" t="inlineStr">
+        <is>
+          <t>Moderate (12)</t>
+        </is>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>Planned on-cycle fix; monitored under vulnerability management.</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L58" s="6" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>Acceptable (BRA)</t>
+        </is>
+      </c>
+      <c r="N58" s="6" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+      <c r="O58" s="3" t="inlineStr">
+        <is>
+          <t>closed-box</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>FND-0057</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>CBT</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>exploitable in deployment (network-reachable): requests 2.19.0: PYSEC-2023-74 (2</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>requests==2.19.0</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr"/>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H59" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I59" s="3" t="inlineStr">
+        <is>
+          <t>Moderate (12)</t>
+        </is>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>Planned on-cycle fix; monitored under vulnerability management.</t>
+        </is>
+      </c>
+      <c r="K59" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L59" s="6" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>Acceptable (BRA)</t>
+        </is>
+      </c>
+      <c r="N59" s="6" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+      <c r="O59" s="3" t="inlineStr">
+        <is>
+          <t>closed-box</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>FND-0058</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>CBT</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">exploitable in deployment (network-reachable): requests 2.19.0: PYSEC-2026-1873 </t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>requests==2.19.0</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr"/>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I60" s="3" t="inlineStr">
+        <is>
+          <t>Moderate (12)</t>
+        </is>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>Planned on-cycle fix; monitored under vulnerability management.</t>
+        </is>
+      </c>
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L60" s="6" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>Acceptable (BRA)</t>
+        </is>
+      </c>
+      <c r="N60" s="6" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+      <c r="O60" s="3" t="inlineStr">
+        <is>
+          <t>closed-box</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>FND-0059</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>CBT</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">exploitable in deployment (network-reachable): requests 2.19.0: PYSEC-2026-1872 </t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>requests==2.19.0</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr"/>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H61" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I61" s="3" t="inlineStr">
+        <is>
+          <t>Moderate (12)</t>
+        </is>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>Planned on-cycle fix; monitored under vulnerability management.</t>
+        </is>
+      </c>
+      <c r="K61" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L61" s="6" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>Acceptable (BRA)</t>
+        </is>
+      </c>
+      <c r="N61" s="6" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+      <c r="O61" s="3" t="inlineStr">
+        <is>
+          <t>closed-box</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>FND-0060</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>CBT</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">exploitable in deployment (network-reachable): requests 2.19.0: PYSEC-2026-2275 </t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>requests==2.19.0</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr"/>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I62" s="3" t="inlineStr">
+        <is>
+          <t>Moderate (12)</t>
+        </is>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>Planned on-cycle fix; monitored under vulnerability management.</t>
+        </is>
+      </c>
+      <c r="K62" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L62" s="6" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>Acceptable (BRA)</t>
+        </is>
+      </c>
+      <c r="N62" s="6" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+      <c r="O62" s="3" t="inlineStr">
+        <is>
+          <t>closed-box</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>TMT-001</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>TMT</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>command -v clevis || echo missing</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>CWE-311</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H63" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I63" s="3" t="inlineStr">
+        <is>
+          <t>Moderate (12)</t>
+        </is>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>Planned on-cycle fix; monitored under vulnerability management.</t>
+        </is>
+      </c>
+      <c r="K63" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L63" s="6" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>Acceptable (BRA)</t>
+        </is>
+      </c>
+      <c r="N63" s="6" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+      <c r="O63" s="3" t="inlineStr">
+        <is>
+          <t>TMT-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
           <t>TMT-002</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B64" s="3" t="inlineStr">
         <is>
           <t>TMT</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C64" s="3" t="inlineStr">
         <is>
           <t>missing</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D64" s="3" t="inlineStr">
         <is>
           <t>command -v auditctl || echo missing</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E64" s="3" t="inlineStr">
         <is>
           <t>CWE-778</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="n">
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="I18" s="3" t="inlineStr">
+      <c r="I64" s="3" t="inlineStr">
         <is>
           <t>Moderate (9)</t>
         </is>
       </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>Planned on-cycle fix; monitored under vulnerability management.</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="L18" s="6" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="M18" s="3" t="inlineStr">
-        <is>
-          <t>Acceptable (BRA)</t>
-        </is>
-      </c>
-      <c r="N18" s="6" t="inlineStr">
-        <is>
-          <t>Applicable</t>
-        </is>
-      </c>
-      <c r="O18" s="3" t="inlineStr">
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>Planned on-cycle fix; monitored under vulnerability management.</t>
+        </is>
+      </c>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L64" s="6" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>Acceptable (BRA)</t>
+        </is>
+      </c>
+      <c r="N64" s="6" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+      <c r="O64" s="3" t="inlineStr">
         <is>
           <t>TMT-002</t>
         </is>
